--- a/05_Figures/Proteome_T2/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Proteome_T2/F1_Overview/c_data/f1_overview.xlsx
@@ -104,16 +104,16 @@
     <t>Participant identifier.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>hr_lr</t>
+  </si>
+  <si>
+    <t>The study's HR or LR label, shown beside a cluster grouping's own group.</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
-    <t>Group the row belongs to (HR, LR, Hi, Lo, C1, C2), or a group cell such as HR_T1.</t>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>cluster</t>
@@ -200,7 +200,7 @@
     <t>Time window or pairing: training (T2 - T1), acute (T3 - T2), baseline (T1 level against later change), baseline_level, post_level, post_bout_level (a level against trait levels); all or a time point in PERMANOVA.</t>
   </si>
   <si>
-    <t>arms</t>
+    <t>groups</t>
   </si>
   <si>
     <t>Groups included in the test.</t>
@@ -860,7 +860,7 @@
     <t>03_Group_comparisons/Proteome_T2/c_data/02_protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>61268dafba03a8b85fdfa8cd7396381c</t>
+    <t>6b3e7f277510999ce920139a4cdf09f5</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -884,13 +884,13 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>02_Groups/Proteome_T2/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>f4dabcec04bf30833e381b0858deefc2</t>
+    <t>24ce0b5aee6a397d70072cc1047b09c4</t>
   </si>
   <si>
     <t>design</t>
@@ -899,7 +899,7 @@
     <t>03_Group_comparisons/Proteome_T2/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>ec109143c9337576f3039e2d1550a7c0</t>
+    <t>8ea3f088a35b7fea575e289be5d64c01</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -2872,10 +2872,10 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2905,10 +2905,10 @@
         <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -4064,7 +4064,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>50</v>
@@ -4965,7 +4965,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>50</v>
@@ -5745,7 +5745,7 @@
         <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>189</v>
@@ -5771,7 +5771,7 @@
         <v>183</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>129</v>
@@ -5797,7 +5797,7 @@
         <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>153</v>
@@ -5823,7 +5823,7 @@
         <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>122</v>
